--- a/output/daily_ratings/uk_ratings_2026-05-01.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-05-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P178"/>
+  <dimension ref="A1:P243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7777,51 +7777,51 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Earth Shot (IRE)</t>
+          <t>Central Command (IRE)</t>
         </is>
       </c>
       <c r="I124" t="n">
         <v>3</v>
       </c>
       <c r="J124" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N124" t="n">
-        <v>57.2</v>
+        <v>49.4</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -7835,53 +7835,53 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G125" t="n">
         <v>2</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Velvet Vega (IRE)</t>
+          <t>Fallacious Promise</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M125" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N125" t="n">
-        <v>47.4</v>
+        <v>33.1</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -7895,53 +7895,53 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G126" t="n">
         <v>3</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Wild Violet (FR)</t>
+          <t>Project Kinsman (USA)</t>
         </is>
       </c>
       <c r="I126" t="n">
         <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L126" t="n">
-        <v>9.75</v>
+        <v>6.25</v>
       </c>
       <c r="M126" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N126" t="n">
-        <v>38.8</v>
+        <v>19.2</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -7949,59 +7949,59 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G127" t="n">
         <v>4</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Blue Noon (IRE)</t>
+          <t>Regal Knight</t>
         </is>
       </c>
       <c r="I127" t="n">
         <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L127" t="n">
-        <v>9.800000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="M127" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N127" t="n">
-        <v>39.9</v>
+        <v>23</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -8009,59 +8009,59 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G128" t="n">
         <v>5</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Malika</t>
+          <t>Steel Fixer</t>
         </is>
       </c>
       <c r="I128" t="n">
         <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L128" t="n">
-        <v>17.8</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M128" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N128" t="n">
-        <v>14.6</v>
+        <v>21.4</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -8069,100 +8069,100 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G129" t="n">
         <v>6</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Mokata</t>
+          <t>Sweet Love</t>
         </is>
       </c>
       <c r="I129" t="n">
         <v>3</v>
       </c>
       <c r="J129" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L129" t="n">
-        <v>28.8</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M129" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N129" t="n">
-        <v>14</v>
+        <v>21.5</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G130" t="n">
         <v>7</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Anthena</t>
+          <t>Ballon Rouge</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -8172,74 +8172,76 @@
         <v>127</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L130" t="n">
-        <v>52.8</v>
+        <v>10.78</v>
       </c>
       <c r="M130" t="n">
-        <v>126.46</v>
+        <v>136.01</v>
       </c>
       <c r="N130" t="n">
-        <v>-27.9</v>
+        <v>18.3</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Ancient Egypt (IRE)</t>
+          <t>Skirt Around (USA)</t>
         </is>
       </c>
       <c r="I131" t="n">
         <v>3</v>
       </c>
       <c r="J131" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K131" t="n">
-        <v>93</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L131" t="n">
+        <v>10.88</v>
+      </c>
       <c r="M131" t="n">
-        <v>123.8</v>
+        <v>136.01</v>
       </c>
       <c r="N131" t="n">
-        <v>77.5</v>
+        <v>25.1</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8247,59 +8249,57 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>2</v>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F132" t="n">
+        <v>5</v>
+      </c>
+      <c r="G132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="n">
-        <v>2</v>
-      </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>My Love Is King</t>
+          <t>Star Cast</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J132" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K132" t="n">
-        <v>95</v>
-      </c>
-      <c r="L132" t="n">
-        <v>2</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
-        <v>123.8</v>
+        <v>134.05</v>
       </c>
       <c r="N132" t="n">
-        <v>72.8</v>
+        <v>44.2</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8307,179 +8307,179 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>2</v>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F133" t="n">
+        <v>5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Say What You See (IRE)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>4</v>
+      </c>
+      <c r="J133" t="n">
+        <v>135</v>
+      </c>
+      <c r="K133" t="n">
+        <v>75</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M133" t="n">
+        <v>134.05</v>
+      </c>
+      <c r="N133" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
         <v>1</v>
-      </c>
-      <c r="G133" t="n">
-        <v>3</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Archers Bay (IRE)</t>
-        </is>
-      </c>
-      <c r="I133" t="n">
-        <v>3</v>
-      </c>
-      <c r="J133" t="n">
-        <v>128</v>
-      </c>
-      <c r="K133" t="n">
-        <v>93</v>
-      </c>
-      <c r="L133" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M133" t="n">
-        <v>123.8</v>
-      </c>
-      <c r="N133" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>2</v>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F134" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Haveyoumissedme</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>8</v>
+      </c>
+      <c r="J134" t="n">
+        <v>133</v>
+      </c>
+      <c r="K134" t="n">
+        <v>73</v>
+      </c>
+      <c r="L134" t="n">
+        <v>3</v>
+      </c>
+      <c r="M134" t="n">
+        <v>134.05</v>
+      </c>
+      <c r="N134" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
         <v>1</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Lyneham (IRE)</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
-        <v>3</v>
-      </c>
-      <c r="J134" t="n">
-        <v>128</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M134" t="n">
-        <v>123.8</v>
-      </c>
-      <c r="N134" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Poseidons Warrior (IRE)</t>
+          <t>Jack Sparowe (IRE)</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K135" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="L135" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M135" t="n">
-        <v>123.8</v>
+        <v>134.05</v>
       </c>
       <c r="N135" t="n">
-        <v>50.5</v>
+        <v>36.2</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -8487,57 +8487,59 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>St Anton (IRE)</t>
+          <t>King Of Fury (IRE)</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J136" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K136" t="n">
-        <v>82</v>
-      </c>
-      <c r="L136" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5.25</v>
+      </c>
       <c r="M136" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N136" t="n">
-        <v>75.7</v>
+        <v>42.4</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -8545,59 +8547,59 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Comic Hero (IRE)</t>
+          <t>Free Speech (IRE)</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K137" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L137" t="n">
-        <v>0.15</v>
+        <v>5.35</v>
       </c>
       <c r="M137" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N137" t="n">
-        <v>71.90000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -8605,59 +8607,59 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G138" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Fort Rock</t>
+          <t>Sea The Light (IRE)</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>135</v>
       </c>
       <c r="K138" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="L138" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M138" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N138" t="n">
-        <v>76.3</v>
+        <v>44.3</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -8665,59 +8667,59 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C139" t="n">
+        <v>10.19090909090909</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
         <v>8</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>3</v>
-      </c>
-      <c r="G139" t="n">
-        <v>4</v>
-      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lake Como (IRE)</t>
+          <t>Mao Shang Wong (IRE)</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J139" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K139" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="L139" t="n">
-        <v>3.15</v>
+        <v>6.25</v>
       </c>
       <c r="M139" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N139" t="n">
-        <v>73.2</v>
+        <v>41.9</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -8731,53 +8733,53 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G140" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Elan Dor</t>
+          <t>Natzor (FR)</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J140" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K140" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L140" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="M140" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N140" t="n">
-        <v>72.8</v>
+        <v>38.3</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -8791,53 +8793,53 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Objector (IRE)</t>
+          <t>Sure And Stedfast (IRE)</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K141" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="L141" t="n">
-        <v>5.949999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="M141" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N141" t="n">
-        <v>65.7</v>
+        <v>32.9</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8845,59 +8847,59 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Vincenzo Peruggia (IRE)</t>
+          <t>Jujubella (IRE)</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J142" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K142" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L142" t="n">
-        <v>6.1</v>
+        <v>11.15</v>
       </c>
       <c r="M142" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N142" t="n">
-        <v>65.90000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -8905,233 +8907,233 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>10.19090909090909</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Royal Bodyguard (IRE)</t>
+          <t>Sound Janet</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J143" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K143" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L143" t="n">
-        <v>7.35</v>
+        <v>26.15</v>
       </c>
       <c r="M143" t="n">
-        <v>98.33</v>
+        <v>134.05</v>
       </c>
       <c r="N143" t="n">
-        <v>47.7</v>
+        <v>14.2</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>3</v>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G144" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Zennor Storm</t>
+          <t>Havachoc</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="K144" t="n">
-        <v>91</v>
-      </c>
-      <c r="L144" t="n">
-        <v>11.1</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>98.33</v>
-      </c>
-      <c r="N144" t="n">
-        <v>53.4</v>
-      </c>
+        <v>163.05</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
-        <v>12</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F145" t="n">
+        <v>4</v>
+      </c>
+      <c r="G145" t="n">
         <v>1</v>
       </c>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bay City Roller (IRE)</t>
+          <t>The Cursor</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>4</v>
       </c>
       <c r="J145" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K145" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
-        <v>152.38</v>
-      </c>
-      <c r="N145" t="inlineStr"/>
+        <v>163.05</v>
+      </c>
+      <c r="N145" t="n">
+        <v>65.40000000000001</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>12</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Santorini Star (IRE)</t>
+          <t>New York Minute (IRE)</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K146" t="n">
-        <v>107</v>
-      </c>
-      <c r="L146" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L146" t="n">
+        <v>11</v>
+      </c>
       <c r="M146" t="n">
-        <v>152.38</v>
+        <v>163.05</v>
       </c>
       <c r="N146" t="n">
-        <v>63.7</v>
+        <v>42.1</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9139,59 +9141,59 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C147" t="n">
-        <v>12</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Eydon (IRE)</t>
+          <t>Machete (FR)</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>7</v>
       </c>
       <c r="J147" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K147" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="L147" t="n">
-        <v>1.25</v>
+        <v>15.25</v>
       </c>
       <c r="M147" t="n">
-        <v>152.38</v>
+        <v>163.05</v>
       </c>
       <c r="N147" t="n">
-        <v>63.3</v>
+        <v>33</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9199,179 +9201,177 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>French Master (IRE)</t>
+          <t>Ludos Landing (IRE)</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J148" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K148" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="L148" t="n">
-        <v>1.75</v>
+        <v>21.25</v>
       </c>
       <c r="M148" t="n">
-        <v>152.38</v>
+        <v>163.05</v>
       </c>
       <c r="N148" t="n">
-        <v>64.40000000000001</v>
+        <v>24.5</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C149" t="n">
-        <v>12</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sunway (FR)</t>
+          <t>Melinda (IRE)</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>5</v>
       </c>
       <c r="J149" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="K149" t="n">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="L149" t="n">
-        <v>1.8</v>
+        <v>22.25</v>
       </c>
       <c r="M149" t="n">
-        <v>152.38</v>
+        <v>163.05</v>
       </c>
       <c r="N149" t="n">
-        <v>64.7</v>
+        <v>15</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>4</v>
       </c>
       <c r="C150" t="n">
-        <v>12</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F150" t="n">
+        <v>4</v>
+      </c>
+      <c r="G150" t="n">
         <v>1</v>
       </c>
-      <c r="G150" t="n">
-        <v>5</v>
-      </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Paradias (GER)</t>
+          <t>Khaleejy (IRE)</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="K150" t="n">
-        <v>105</v>
-      </c>
-      <c r="L150" t="n">
-        <v>2.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>152.38</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N150" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -9385,53 +9385,53 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>4</v>
       </c>
       <c r="C151" t="n">
-        <v>12</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lions Pride</t>
+          <t>Grasmere Boy</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K151" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>18.55</v>
+        <v>0.15</v>
       </c>
       <c r="M151" t="n">
-        <v>152.38</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N151" t="n">
-        <v>32.2</v>
+        <v>45.3</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -9439,169 +9439,179 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Benacre (IRE)</t>
+          <t>Viper</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K152" t="n">
-        <v>79</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.3</v>
+      </c>
       <c r="M152" t="n">
-        <v>84.31999999999999</v>
-      </c>
-      <c r="N152" t="inlineStr"/>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="N152" t="n">
+        <v>45.5</v>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>-7.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Shah (IRE)</t>
+          <t>Eklleem</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K153" t="n">
-        <v>89</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1.3</v>
+      </c>
       <c r="M153" t="n">
-        <v>84.31999999999999</v>
-      </c>
-      <c r="N153" t="inlineStr"/>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="N153" t="n">
+        <v>42.2</v>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Billyjoh</t>
+          <t>Marhayb</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>125</v>
       </c>
       <c r="K154" t="n">
-        <v>90</v>
-      </c>
-      <c r="L154" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M154" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N154" t="n">
-        <v>64.8</v>
+        <v>35.7</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9615,53 +9625,53 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Golden Redemption (USA)</t>
+          <t>Eljowhary</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J155" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="K155" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M155" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N155" t="n">
-        <v>51</v>
+        <v>40.5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -9669,59 +9679,59 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>4</v>
+      </c>
+      <c r="G156" t="n">
         <v>7</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>3</v>
-      </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Silver Ghost (IRE)</t>
+          <t>Thunder Rush</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K156" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>2.75</v>
+        <v>10.8</v>
       </c>
       <c r="M156" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N156" t="n">
-        <v>59.1</v>
+        <v>12.7</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9735,53 +9745,53 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Elarak</t>
+          <t>Record Day</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K157" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>4</v>
+        <v>11.3</v>
       </c>
       <c r="M157" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N157" t="n">
-        <v>66.5</v>
+        <v>10.7</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9789,59 +9799,59 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G158" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Misunderstood (FR)</t>
+          <t>Billyjoegold</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>4</v>
       </c>
       <c r="J158" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="K158" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>9</v>
+        <v>17.3</v>
       </c>
       <c r="M158" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N158" t="n">
-        <v>41.2</v>
+        <v>-5.5</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9855,53 +9865,53 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C159" t="n">
-        <v>7</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G159" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Leadman</t>
+          <t>Furrst Lady (IRE)</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J159" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K159" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>12.75</v>
+        <v>17.8</v>
       </c>
       <c r="M159" t="n">
-        <v>84.31999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N159" t="n">
-        <v>22.7</v>
+        <v>-15.3</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -9915,51 +9925,51 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="n">
         <v>6</v>
       </c>
-      <c r="C160" t="n">
-        <v>7</v>
-      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Saber Strike (IRE)</t>
+          <t>Starmade (IRE)</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>3</v>
       </c>
       <c r="J160" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N160" t="n">
-        <v>72.5</v>
+        <v>58</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -9973,53 +9983,53 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="n">
         <v>6</v>
       </c>
-      <c r="C161" t="n">
-        <v>7</v>
-      </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G161" t="n">
         <v>2</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cerro Blanco</t>
+          <t>Dandy Breeze (IRE)</t>
         </is>
       </c>
       <c r="I161" t="n">
         <v>3</v>
       </c>
       <c r="J161" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L161" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="M161" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N161" t="n">
-        <v>70.09999999999999</v>
+        <v>51.6</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -10033,53 +10043,53 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="n">
         <v>6</v>
       </c>
-      <c r="C162" t="n">
-        <v>7</v>
-      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G162" t="n">
         <v>3</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Stellar Sunrise</t>
+          <t>Theres A Chance (IRE)</t>
         </is>
       </c>
       <c r="I162" t="n">
         <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K162" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="L162" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="M162" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N162" t="n">
-        <v>62</v>
+        <v>43.9</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -10093,53 +10103,53 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B163" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" t="n">
         <v>6</v>
       </c>
-      <c r="C163" t="n">
-        <v>7</v>
-      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G163" t="n">
         <v>4</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Ellusive Butterfly (IRE)</t>
+          <t>Stoic Poet (IRE)</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>3</v>
       </c>
       <c r="J163" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K163" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="L163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M163" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N163" t="n">
-        <v>56.2</v>
+        <v>34.8</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10147,40 +10157,40 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B164" t="n">
+        <v>5</v>
+      </c>
+      <c r="C164" t="n">
         <v>6</v>
       </c>
-      <c r="C164" t="n">
-        <v>7</v>
-      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G164" t="n">
         <v>5</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Maximized</t>
+          <t>Loquella (IRE)</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -10190,16 +10200,16 @@
         <v>131</v>
       </c>
       <c r="K164" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="L164" t="n">
-        <v>8.75</v>
+        <v>5</v>
       </c>
       <c r="M164" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N164" t="n">
-        <v>52.2</v>
+        <v>39.4</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10207,59 +10217,59 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B165" t="n">
+        <v>5</v>
+      </c>
+      <c r="C165" t="n">
         <v>6</v>
       </c>
-      <c r="C165" t="n">
-        <v>7</v>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G165" t="n">
         <v>6</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Jel Pepper (IRE)</t>
+          <t>Logi Bear (IRE)</t>
         </is>
       </c>
       <c r="I165" t="n">
         <v>3</v>
       </c>
       <c r="J165" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K165" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="L165" t="n">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="M165" t="n">
-        <v>85.52</v>
+        <v>74.27</v>
       </c>
       <c r="N165" t="n">
-        <v>42.4</v>
+        <v>22.6</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10273,223 +10283,227 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C166" t="n">
         <v>6</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Angel Love</t>
+          <t>Numero Vingt</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>3</v>
       </c>
       <c r="J166" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K166" t="n">
-        <v>83</v>
-      </c>
-      <c r="L166" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="L166" t="n">
+        <v>10.5</v>
+      </c>
       <c r="M166" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="N166" t="inlineStr"/>
+        <v>74.27</v>
+      </c>
+      <c r="N166" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C167" t="n">
         <v>6</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Mercury Day (IRE)</t>
+          <t>Yy Spirit (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K167" t="n">
-        <v>78</v>
-      </c>
-      <c r="L167" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="L167" t="n">
+        <v>17.5</v>
+      </c>
       <c r="M167" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="N167" t="inlineStr"/>
+        <v>74.27</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-15.3</v>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Rich Rhythm</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
         <v>7</v>
       </c>
-      <c r="C168" t="n">
-        <v>6</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>3</v>
-      </c>
-      <c r="G168" t="n">
-        <v>1</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Cinque Verde</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>6</v>
-      </c>
       <c r="J168" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="K168" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="N168" t="n">
-        <v>83.7</v>
-      </c>
+        <v>88.22</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Lady Kodiac (IRE)</t>
+          <t>Beale Street</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
         <v>133</v>
       </c>
       <c r="K169" t="n">
-        <v>88</v>
-      </c>
-      <c r="L169" t="n">
-        <v>6.5</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N169" t="n">
-        <v>70.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -10497,59 +10511,59 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Powdering (IRE)</t>
+          <t>Recency Bias (IRE)</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J170" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K170" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L170" t="n">
-        <v>9</v>
+        <v>0.15</v>
       </c>
       <c r="M170" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N170" t="n">
-        <v>58</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -10557,59 +10571,59 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B171" t="n">
+        <v>6</v>
+      </c>
+      <c r="C171" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>4</v>
+      </c>
+      <c r="G171" t="n">
+        <v>3</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>The Green Man (IRE)</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
         <v>7</v>
       </c>
-      <c r="C171" t="n">
-        <v>6</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>3</v>
-      </c>
-      <c r="G171" t="n">
-        <v>4</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Paradise Walk (IRE)</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>3</v>
-      </c>
       <c r="J171" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K171" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L171" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="M171" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N171" t="n">
-        <v>54.7</v>
+        <v>49.4</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10623,53 +10637,53 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Anaisa</t>
+          <t>Blufferonthebus (IRE)</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J172" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K172" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="L172" t="n">
-        <v>9.25</v>
+        <v>2.5</v>
       </c>
       <c r="M172" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N172" t="n">
-        <v>60</v>
+        <v>41.4</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -10677,59 +10691,59 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Orchid (IRE)</t>
+          <t>Pressures On (FR)</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="K173" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L173" t="n">
-        <v>10.25</v>
+        <v>3.25</v>
       </c>
       <c r="M173" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N173" t="n">
-        <v>54</v>
+        <v>52.3</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10737,59 +10751,59 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C174" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>4</v>
+      </c>
+      <c r="G174" t="n">
         <v>6</v>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>3</v>
-      </c>
-      <c r="G174" t="n">
-        <v>7</v>
-      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lady Roxby</t>
+          <t>Gressington (IRE)</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J174" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K174" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L174" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="M174" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N174" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10797,44 +10811,44 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B175" t="n">
+        <v>6</v>
+      </c>
+      <c r="C175" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>4</v>
+      </c>
+      <c r="G175" t="n">
         <v>7</v>
       </c>
-      <c r="C175" t="n">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>William Dewhirst (IRE)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
         <v>6</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>3</v>
-      </c>
-      <c r="G175" t="n">
-        <v>8</v>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Cuban Lady</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>4</v>
       </c>
       <c r="J175" t="n">
         <v>131</v>
@@ -10843,13 +10857,13 @@
         <v>76</v>
       </c>
       <c r="L175" t="n">
-        <v>11.6</v>
+        <v>4.55</v>
       </c>
       <c r="M175" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N175" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10857,59 +10871,59 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B176" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>4</v>
+      </c>
+      <c r="G176" t="n">
+        <v>8</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ey Up Its Jazz</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
         <v>7</v>
       </c>
-      <c r="C176" t="n">
-        <v>6</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>3</v>
-      </c>
-      <c r="G176" t="n">
-        <v>9</v>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Lightning Polka</t>
-        </is>
-      </c>
-      <c r="I176" t="n">
-        <v>3</v>
-      </c>
       <c r="J176" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K176" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L176" t="n">
-        <v>12.35</v>
+        <v>15.55</v>
       </c>
       <c r="M176" t="n">
-        <v>71.43000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="N176" t="n">
-        <v>42.9</v>
+        <v>2.7</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10917,13 +10931,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -10934,42 +10948,40 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G177" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Slay Queen (IRE)</t>
+          <t>Raft Up (IRE)</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
         <v>133</v>
       </c>
       <c r="K177" t="n">
-        <v>88</v>
-      </c>
-      <c r="L177" t="n">
-        <v>14.85</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
       <c r="M177" t="n">
-        <v>71.43000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="N177" t="n">
-        <v>42</v>
+        <v>60.6</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -10977,13 +10989,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NEWMARKET (ROWLEY)</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -10994,49 +11006,3915 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>5</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Lions House</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>5</v>
+      </c>
+      <c r="J178" t="n">
+        <v>134</v>
+      </c>
+      <c r="K178" t="n">
+        <v>69</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M178" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N178" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>7</v>
+      </c>
+      <c r="C179" t="n">
+        <v>6</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Woolridge</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" t="n">
+        <v>128</v>
+      </c>
+      <c r="K179" t="n">
+        <v>63</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M179" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N179" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>7</v>
+      </c>
+      <c r="C180" t="n">
+        <v>6</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>5</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Annie Edson Taylor</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>5</v>
+      </c>
+      <c r="J180" t="n">
+        <v>129</v>
+      </c>
+      <c r="K180" t="n">
+        <v>64</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M180" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N180" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>7</v>
+      </c>
+      <c r="C181" t="n">
+        <v>6</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>5</v>
+      </c>
+      <c r="G181" t="n">
+        <v>5</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Caragio (IRE)</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>6</v>
+      </c>
+      <c r="J181" t="n">
+        <v>136</v>
+      </c>
+      <c r="K181" t="n">
+        <v>71</v>
+      </c>
+      <c r="L181" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M181" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N181" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>7</v>
+      </c>
+      <c r="C182" t="n">
+        <v>6</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>5</v>
+      </c>
+      <c r="G182" t="n">
+        <v>6</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kings Merchant</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>5</v>
+      </c>
+      <c r="J182" t="n">
+        <v>132</v>
+      </c>
+      <c r="K182" t="n">
+        <v>67</v>
+      </c>
+      <c r="L182" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M182" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N182" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>7</v>
+      </c>
+      <c r="C183" t="n">
+        <v>6</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" t="n">
+        <v>7</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Lord Abama (IRE)</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>7</v>
+      </c>
+      <c r="J183" t="n">
+        <v>129</v>
+      </c>
+      <c r="K183" t="n">
+        <v>64</v>
+      </c>
+      <c r="L183" t="n">
+        <v>4</v>
+      </c>
+      <c r="M183" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N183" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" t="n">
+        <v>6</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>5</v>
+      </c>
+      <c r="G184" t="n">
+        <v>8</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Asadjumeirah</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>116</v>
+      </c>
+      <c r="K184" t="n">
+        <v>51</v>
+      </c>
+      <c r="L184" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M184" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N184" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>7</v>
+      </c>
+      <c r="C185" t="n">
+        <v>6</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>5</v>
+      </c>
+      <c r="G185" t="n">
+        <v>9</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Goal Line (IRE)</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>128</v>
+      </c>
+      <c r="K185" t="n">
+        <v>63</v>
+      </c>
+      <c r="L185" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M185" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N185" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" t="n">
+        <v>6</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>5</v>
+      </c>
+      <c r="G186" t="n">
+        <v>10</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bellagio Man (IRE)</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>130</v>
+      </c>
+      <c r="K186" t="n">
+        <v>65</v>
+      </c>
+      <c r="L186" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M186" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N186" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>7</v>
+      </c>
+      <c r="C187" t="n">
+        <v>6</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>5</v>
+      </c>
+      <c r="G187" t="n">
+        <v>11</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Speeding Bullet (IRE)</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J187" t="n">
+        <v>135</v>
+      </c>
+      <c r="K187" t="n">
+        <v>70</v>
+      </c>
+      <c r="L187" t="n">
+        <v>14</v>
+      </c>
+      <c r="M187" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N187" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" t="n">
+        <v>6</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>5</v>
+      </c>
+      <c r="G188" t="n">
+        <v>12</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Invincible Ruby (IRE)</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>4</v>
+      </c>
+      <c r="J188" t="n">
+        <v>133</v>
+      </c>
+      <c r="K188" t="n">
+        <v>68</v>
+      </c>
+      <c r="L188" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M188" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="N188" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>10</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>2</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Earth Shot (IRE)</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>3</v>
+      </c>
+      <c r="J189" t="n">
+        <v>127</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N189" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>10</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Velvet Vega (IRE)</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>3</v>
+      </c>
+      <c r="J190" t="n">
+        <v>127</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>5</v>
+      </c>
+      <c r="M190" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N190" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>10</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Wild Violet (FR)</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>3</v>
+      </c>
+      <c r="J191" t="n">
+        <v>127</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M191" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N191" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="n">
+        <v>10</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Blue Noon (IRE)</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>3</v>
+      </c>
+      <c r="J192" t="n">
+        <v>127</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M192" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N192" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>10</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>5</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Malika</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>3</v>
+      </c>
+      <c r="J193" t="n">
+        <v>127</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M193" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N193" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>10</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>2</v>
+      </c>
+      <c r="G194" t="n">
+        <v>6</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Mokata</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>3</v>
+      </c>
+      <c r="J194" t="n">
+        <v>127</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="M194" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N194" t="n">
+        <v>14</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>10</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" t="n">
+        <v>7</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Anthena</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>3</v>
+      </c>
+      <c r="J195" t="n">
+        <v>127</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="M195" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2</v>
+      </c>
+      <c r="C196" t="n">
+        <v>10</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>Good To Firm</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>3</v>
-      </c>
-      <c r="G178" t="n">
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Ancient Egypt (IRE)</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>3</v>
+      </c>
+      <c r="J196" t="n">
+        <v>128</v>
+      </c>
+      <c r="K196" t="n">
+        <v>93</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="N196" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2</v>
+      </c>
+      <c r="C197" t="n">
+        <v>10</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>2</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>My Love Is King</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>128</v>
+      </c>
+      <c r="K197" t="n">
+        <v>95</v>
+      </c>
+      <c r="L197" t="n">
+        <v>2</v>
+      </c>
+      <c r="M197" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="N197" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2</v>
+      </c>
+      <c r="C198" t="n">
+        <v>10</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Archers Bay (IRE)</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>128</v>
+      </c>
+      <c r="K198" t="n">
+        <v>93</v>
+      </c>
+      <c r="L198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M198" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="N198" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2</v>
+      </c>
+      <c r="C199" t="n">
+        <v>10</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>4</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Lyneham (IRE)</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>3</v>
+      </c>
+      <c r="J199" t="n">
+        <v>128</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M199" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="N199" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C200" t="n">
+        <v>10</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Poseidons Warrior (IRE)</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>3</v>
+      </c>
+      <c r="J200" t="n">
+        <v>128</v>
+      </c>
+      <c r="K200" t="n">
+        <v>109</v>
+      </c>
+      <c r="L200" t="n">
         <v>11</v>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="M200" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="N200" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>3</v>
+      </c>
+      <c r="C201" t="n">
+        <v>8</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>St Anton (IRE)</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>3</v>
+      </c>
+      <c r="J201" t="n">
+        <v>127</v>
+      </c>
+      <c r="K201" t="n">
+        <v>82</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N201" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>3</v>
+      </c>
+      <c r="C202" t="n">
+        <v>8</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>3</v>
+      </c>
+      <c r="G202" t="n">
+        <v>2</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Comic Hero (IRE)</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" t="n">
+        <v>123</v>
+      </c>
+      <c r="K202" t="n">
+        <v>78</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M202" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N202" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>3</v>
+      </c>
+      <c r="C203" t="n">
+        <v>8</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+      <c r="G203" t="n">
+        <v>3</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Fort Rock</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>3</v>
+      </c>
+      <c r="J203" t="n">
+        <v>135</v>
+      </c>
+      <c r="K203" t="n">
+        <v>90</v>
+      </c>
+      <c r="L203" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M203" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N203" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="n">
+        <v>8</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>3</v>
+      </c>
+      <c r="G204" t="n">
+        <v>4</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Lake Como (IRE)</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>3</v>
+      </c>
+      <c r="J204" t="n">
+        <v>134</v>
+      </c>
+      <c r="K204" t="n">
+        <v>89</v>
+      </c>
+      <c r="L204" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M204" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N204" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>3</v>
+      </c>
+      <c r="C205" t="n">
+        <v>8</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>3</v>
+      </c>
+      <c r="G205" t="n">
+        <v>5</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Elan Dor</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>3</v>
+      </c>
+      <c r="J205" t="n">
+        <v>134</v>
+      </c>
+      <c r="K205" t="n">
+        <v>89</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M205" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N205" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>3</v>
+      </c>
+      <c r="C206" t="n">
+        <v>8</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" t="n">
+        <v>6</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Objector (IRE)</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>3</v>
+      </c>
+      <c r="J206" t="n">
+        <v>135</v>
+      </c>
+      <c r="K206" t="n">
+        <v>90</v>
+      </c>
+      <c r="L206" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="M206" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N206" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>3</v>
+      </c>
+      <c r="C207" t="n">
+        <v>8</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>3</v>
+      </c>
+      <c r="G207" t="n">
+        <v>7</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Vincenzo Peruggia (IRE)</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>3</v>
+      </c>
+      <c r="J207" t="n">
+        <v>137</v>
+      </c>
+      <c r="K207" t="n">
+        <v>92</v>
+      </c>
+      <c r="L207" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N207" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>3</v>
+      </c>
+      <c r="C208" t="n">
+        <v>8</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>8</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Royal Bodyguard (IRE)</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>3</v>
+      </c>
+      <c r="J208" t="n">
+        <v>116</v>
+      </c>
+      <c r="K208" t="n">
+        <v>71</v>
+      </c>
+      <c r="L208" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="M208" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N208" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>3</v>
+      </c>
+      <c r="C209" t="n">
+        <v>8</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" t="n">
+        <v>9</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Zennor Storm</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>3</v>
+      </c>
+      <c r="J209" t="n">
+        <v>136</v>
+      </c>
+      <c r="K209" t="n">
+        <v>91</v>
+      </c>
+      <c r="L209" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="N209" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>4</v>
+      </c>
+      <c r="C210" t="n">
+        <v>12</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Bay City Roller (IRE)</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>4</v>
+      </c>
+      <c r="J210" t="n">
+        <v>134</v>
+      </c>
+      <c r="K210" t="n">
+        <v>117</v>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>4</v>
+      </c>
+      <c r="C211" t="n">
+        <v>12</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Santorini Star (IRE)</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>5</v>
+      </c>
+      <c r="J211" t="n">
+        <v>128</v>
+      </c>
+      <c r="K211" t="n">
+        <v>107</v>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N211" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>4</v>
+      </c>
+      <c r="C212" t="n">
+        <v>12</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Eydon (IRE)</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>7</v>
+      </c>
+      <c r="J212" t="n">
+        <v>131</v>
+      </c>
+      <c r="K212" t="n">
+        <v>114</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M212" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N212" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" t="n">
+        <v>12</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>French Master (IRE)</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>5</v>
+      </c>
+      <c r="J213" t="n">
+        <v>131</v>
+      </c>
+      <c r="K213" t="n">
+        <v>108</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M213" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N213" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>4</v>
+      </c>
+      <c r="C214" t="n">
+        <v>12</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>4</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sunway (FR)</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>5</v>
+      </c>
+      <c r="J214" t="n">
+        <v>131</v>
+      </c>
+      <c r="K214" t="n">
+        <v>112</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M214" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N214" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" t="n">
+        <v>12</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Paradias (GER)</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>7</v>
+      </c>
+      <c r="J215" t="n">
+        <v>131</v>
+      </c>
+      <c r="K215" t="n">
+        <v>105</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M215" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N215" t="n">
+        <v>63</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>4</v>
+      </c>
+      <c r="C216" t="n">
+        <v>12</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>6</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Lions Pride</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>6</v>
+      </c>
+      <c r="J216" t="n">
+        <v>131</v>
+      </c>
+      <c r="K216" t="n">
+        <v>110</v>
+      </c>
+      <c r="L216" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="M216" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="N216" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>5</v>
+      </c>
+      <c r="C217" t="n">
+        <v>7</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Benacre (IRE)</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>6</v>
+      </c>
+      <c r="J217" t="n">
+        <v>114</v>
+      </c>
+      <c r="K217" t="n">
+        <v>79</v>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>5</v>
+      </c>
+      <c r="C218" t="n">
+        <v>7</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>2</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Shah (IRE)</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>4</v>
+      </c>
+      <c r="J218" t="n">
+        <v>124</v>
+      </c>
+      <c r="K218" t="n">
+        <v>89</v>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>5</v>
+      </c>
+      <c r="C219" t="n">
+        <v>7</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>2</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Billyjoh</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>6</v>
+      </c>
+      <c r="J219" t="n">
+        <v>125</v>
+      </c>
+      <c r="K219" t="n">
+        <v>90</v>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N219" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>5</v>
+      </c>
+      <c r="C220" t="n">
+        <v>7</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Golden Redemption (USA)</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>4</v>
+      </c>
+      <c r="J220" t="n">
+        <v>117</v>
+      </c>
+      <c r="K220" t="n">
+        <v>82</v>
+      </c>
+      <c r="L220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M220" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N220" t="n">
+        <v>51</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>5</v>
+      </c>
+      <c r="C221" t="n">
+        <v>7</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Silver Ghost (IRE)</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>4</v>
+      </c>
+      <c r="J221" t="n">
+        <v>127</v>
+      </c>
+      <c r="K221" t="n">
+        <v>92</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M221" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N221" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>5</v>
+      </c>
+      <c r="C222" t="n">
+        <v>7</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" t="n">
+        <v>4</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Elarak</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>4</v>
+      </c>
+      <c r="J222" t="n">
+        <v>138</v>
+      </c>
+      <c r="K222" t="n">
+        <v>103</v>
+      </c>
+      <c r="L222" t="n">
+        <v>4</v>
+      </c>
+      <c r="M222" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N222" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>5</v>
+      </c>
+      <c r="C223" t="n">
+        <v>7</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Misunderstood (FR)</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>4</v>
+      </c>
+      <c r="J223" t="n">
+        <v>125</v>
+      </c>
+      <c r="K223" t="n">
+        <v>90</v>
+      </c>
+      <c r="L223" t="n">
+        <v>9</v>
+      </c>
+      <c r="M223" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N223" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>7</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>2</v>
+      </c>
+      <c r="G224" t="n">
+        <v>6</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Leadman</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>6</v>
+      </c>
+      <c r="J224" t="n">
+        <v>118</v>
+      </c>
+      <c r="K224" t="n">
+        <v>83</v>
+      </c>
+      <c r="L224" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M224" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="N224" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>6</v>
+      </c>
+      <c r="C225" t="n">
+        <v>7</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Saber Strike (IRE)</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>3</v>
+      </c>
+      <c r="J225" t="n">
+        <v>131</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N225" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>6</v>
+      </c>
+      <c r="C226" t="n">
+        <v>7</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Cerro Blanco</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>3</v>
+      </c>
+      <c r="J226" t="n">
+        <v>131</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M226" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N226" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" t="n">
+        <v>7</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" t="n">
+        <v>3</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Stellar Sunrise</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>3</v>
+      </c>
+      <c r="J227" t="n">
+        <v>131</v>
+      </c>
+      <c r="K227" t="n">
+        <v>103</v>
+      </c>
+      <c r="L227" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M227" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N227" t="n">
+        <v>62</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>6</v>
+      </c>
+      <c r="C228" t="n">
+        <v>7</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" t="n">
+        <v>4</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Ellusive Butterfly (IRE)</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>3</v>
+      </c>
+      <c r="J228" t="n">
+        <v>126</v>
+      </c>
+      <c r="K228" t="n">
+        <v>96</v>
+      </c>
+      <c r="L228" t="n">
+        <v>5</v>
+      </c>
+      <c r="M228" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N228" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>6</v>
+      </c>
+      <c r="C229" t="n">
+        <v>7</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="n">
+        <v>5</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Maximized</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" t="n">
+        <v>131</v>
+      </c>
+      <c r="K229" t="n">
+        <v>98</v>
+      </c>
+      <c r="L229" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M229" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N229" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>6</v>
+      </c>
+      <c r="C230" t="n">
+        <v>7</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>6</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Jel Pepper (IRE)</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>3</v>
+      </c>
+      <c r="J230" t="n">
+        <v>131</v>
+      </c>
+      <c r="K230" t="n">
+        <v>99</v>
+      </c>
+      <c r="L230" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M230" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="N230" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>7</v>
+      </c>
+      <c r="C231" t="n">
+        <v>6</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>3</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Angel Love</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>3</v>
+      </c>
+      <c r="J231" t="n">
+        <v>128</v>
+      </c>
+      <c r="K231" t="n">
+        <v>83</v>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>7</v>
+      </c>
+      <c r="C232" t="n">
+        <v>6</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>3</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Mercury Day (IRE)</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>5</v>
+      </c>
+      <c r="J232" t="n">
+        <v>133</v>
+      </c>
+      <c r="K232" t="n">
+        <v>78</v>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>7</v>
+      </c>
+      <c r="C233" t="n">
+        <v>6</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>3</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Cinque Verde</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>6</v>
+      </c>
+      <c r="J233" t="n">
+        <v>138</v>
+      </c>
+      <c r="K233" t="n">
+        <v>83</v>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N233" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>7</v>
+      </c>
+      <c r="C234" t="n">
+        <v>6</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Lady Kodiac (IRE)</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J234" t="n">
+        <v>133</v>
+      </c>
+      <c r="K234" t="n">
+        <v>88</v>
+      </c>
+      <c r="L234" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M234" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N234" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>7</v>
+      </c>
+      <c r="C235" t="n">
+        <v>6</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>3</v>
+      </c>
+      <c r="G235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Powdering (IRE)</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>6</v>
+      </c>
+      <c r="J235" t="n">
+        <v>134</v>
+      </c>
+      <c r="K235" t="n">
+        <v>79</v>
+      </c>
+      <c r="L235" t="n">
+        <v>9</v>
+      </c>
+      <c r="M235" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N235" t="n">
+        <v>58</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>7</v>
+      </c>
+      <c r="C236" t="n">
+        <v>6</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" t="n">
+        <v>4</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Paradise Walk (IRE)</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>3</v>
+      </c>
+      <c r="J236" t="n">
+        <v>123</v>
+      </c>
+      <c r="K236" t="n">
+        <v>78</v>
+      </c>
+      <c r="L236" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M236" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N236" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>7</v>
+      </c>
+      <c r="C237" t="n">
+        <v>6</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>3</v>
+      </c>
+      <c r="G237" t="n">
+        <v>5</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Anaisa</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>3</v>
+      </c>
+      <c r="J237" t="n">
+        <v>129</v>
+      </c>
+      <c r="K237" t="n">
+        <v>84</v>
+      </c>
+      <c r="L237" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M237" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N237" t="n">
+        <v>60</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>7</v>
+      </c>
+      <c r="C238" t="n">
+        <v>6</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>3</v>
+      </c>
+      <c r="G238" t="n">
+        <v>6</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Orchid (IRE)</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>4</v>
+      </c>
+      <c r="J238" t="n">
+        <v>142</v>
+      </c>
+      <c r="K238" t="n">
+        <v>87</v>
+      </c>
+      <c r="L238" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M238" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N238" t="n">
+        <v>54</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>7</v>
+      </c>
+      <c r="C239" t="n">
+        <v>6</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>3</v>
+      </c>
+      <c r="G239" t="n">
+        <v>7</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Lady Roxby</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>4</v>
+      </c>
+      <c r="J239" t="n">
+        <v>138</v>
+      </c>
+      <c r="K239" t="n">
+        <v>83</v>
+      </c>
+      <c r="L239" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M239" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N239" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>7</v>
+      </c>
+      <c r="C240" t="n">
+        <v>6</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>3</v>
+      </c>
+      <c r="G240" t="n">
+        <v>8</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Cuban Lady</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>4</v>
+      </c>
+      <c r="J240" t="n">
+        <v>131</v>
+      </c>
+      <c r="K240" t="n">
+        <v>76</v>
+      </c>
+      <c r="L240" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M240" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N240" t="n">
+        <v>42</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>7</v>
+      </c>
+      <c r="C241" t="n">
+        <v>6</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G241" t="n">
+        <v>9</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Lightning Polka</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>3</v>
+      </c>
+      <c r="J241" t="n">
+        <v>128</v>
+      </c>
+      <c r="K241" t="n">
+        <v>83</v>
+      </c>
+      <c r="L241" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="M241" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N241" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>7</v>
+      </c>
+      <c r="C242" t="n">
+        <v>6</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>3</v>
+      </c>
+      <c r="G242" t="n">
+        <v>10</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Slay Queen (IRE)</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>3</v>
+      </c>
+      <c r="J242" t="n">
+        <v>133</v>
+      </c>
+      <c r="K242" t="n">
+        <v>88</v>
+      </c>
+      <c r="L242" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="M242" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="N242" t="n">
+        <v>42</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>NEWMARKET (ROWLEY)</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>7</v>
+      </c>
+      <c r="C243" t="n">
+        <v>6</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>3</v>
+      </c>
+      <c r="G243" t="n">
+        <v>11</v>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t>Fantasy Obsessor</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>4</v>
-      </c>
-      <c r="J178" t="n">
+      <c r="I243" t="n">
+        <v>4</v>
+      </c>
+      <c r="J243" t="n">
         <v>123</v>
       </c>
-      <c r="K178" t="n">
+      <c r="K243" t="n">
         <v>68</v>
       </c>
-      <c r="L178" t="n">
+      <c r="L243" t="n">
         <v>14.95</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M243" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="N178" t="n">
+      <c r="N243" t="n">
         <v>27.9</v>
       </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P178" t="n">
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
         <v>0</v>
       </c>
     </row>
